--- a/docs/03_test/DepartmentRepositoryテスト.xlsx
+++ b/docs/03_test/DepartmentRepositoryテスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\fullness\cs-training\Web_App_Exercise\docs\03_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1245D449-7C24-48BE-995C-F53E3D76496B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03554ADA-FD6D-49FD-82E1-49AE84961493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6AC7A638-A2CE-45E1-998B-E596E0F74D78}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" xr2:uid="{6AC7A638-A2CE-45E1-998B-E596E0F74D78}"/>
   </bookViews>
   <sheets>
     <sheet name="部署Repositoryテスト" sheetId="1" r:id="rId1"/>
@@ -490,15 +490,18 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>カバレッジ計測の結果(パーセンテージはLineカバレッジ率)</t>
+    <t>カバレッジ計測の結果(パーセンテージは左がLine coverage、右がBranch coverage)</t>
     <rPh sb="5" eb="7">
       <t>ケイソク</t>
     </rPh>
     <rPh sb="8" eb="10">
       <t>ケッカ</t>
     </rPh>
-    <rPh sb="28" eb="29">
-      <t>リツ</t>
+    <rPh sb="19" eb="20">
+      <t>ヒダリ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ミギ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -658,22 +661,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>120650</xdr:colOff>
+      <xdr:colOff>50077</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:rowOff>35208</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>489329</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>50843</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>514430</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>46485</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85B24676-1B94-933D-1B44-B9EAB3B69354}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70D85B3A-733C-01CC-7542-954695C250EB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -682,21 +685,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="120650" y="7213600"/>
-          <a:ext cx="7372729" cy="838243"/>
+          <a:off x="50077" y="7012170"/>
+          <a:ext cx="8116505" cy="461404"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1537,10 +1534,12 @@
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="E24:H24"/>
     <mergeCell ref="E25:H25"/>
     <mergeCell ref="E26:H26"/>
